--- a/important_mails_2026-10-03.xlsx
+++ b/important_mails_2026-10-03.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
+          <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -533,12 +533,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -548,21 +548,125 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
+          <t>Sat, 3 Oct 2026 03:07:33 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (Jl40SY3EId)</t>
+          <t>Create FBA removal order by 2026-10-15</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-15 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRC8LPGS Quantity: 1
+- FNSKU: B0DRCF83VZ Quantity: 1
+- FNSKU: B0GYPZ58JY Quantity: 1
+- FNSKU: X0022I4RM3 Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid futu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (Jl40SY3EId)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -582,39 +686,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -634,39 +738,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -682,39 +786,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -730,39 +834,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -778,39 +882,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -835,39 +939,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -883,39 +987,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -936,39 +1040,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -988,39 +1092,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1036,39 +1140,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1088,39 +1192,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1140,39 +1244,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1190,39 +1294,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1240,39 +1344,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1290,39 +1394,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -1350,39 +1454,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1401,39 +1505,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1449,106 +1553,6 @@
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
  For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
  To avoid further impact to your account, close or delete any non-compliant listings that you do </t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2227,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 01:10:17 +0000</t>
+          <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2248,410 +2252,11 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+          <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:09:41 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:09:40 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:09:39 +0000</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:09:28 +0000</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:08:10 +0000</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- 4sQeBGpWIe
- Unsellable Products:
-- FNSKU: B0DRCB74YN Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-10-08</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-08 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRC8LPGS Quantity: 1
-- FNSKU: B0DRCC2H56 Quantity: 2
-- FNSKU: B0DRCF83VZ Quantity: 2
-- FNSKU: B0H11DGDRL Quantity: 2
-- FNSKU: X0023C0TBV Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inv</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>A passkey is required for account access starting in two weeks</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -2667,39 +2272,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -2724,39 +2329,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
@@ -2786,39 +2391,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2834,39 +2439,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2882,39 +2487,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2934,39 +2539,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2982,39 +2587,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3030,39 +2635,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -3078,39 +2683,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3126,39 +2731,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3181,39 +2786,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3229,39 +2834,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3277,39 +2882,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3325,39 +2930,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3373,39 +2978,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3421,39 +3026,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3469,39 +3074,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3517,39 +3122,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3565,39 +3170,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3613,39 +3218,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3661,39 +3266,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3709,39 +3314,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3761,39 +3366,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3809,39 +3414,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3857,39 +3462,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3909,39 +3514,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3957,39 +3562,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4005,39 +3610,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4053,39 +3658,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4105,39 +3710,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4153,39 +3758,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -4206,39 +3811,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4258,39 +3863,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4307,39 +3912,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -4355,39 +3960,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -4402,39 +4007,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4454,39 +4059,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 12:34:14 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Registration closes this Friday—save $200 with your exclusive code</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-15/7z5szk3/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5szk6/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
@@ -4500,39 +4105,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -4546,39 +4151,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4598,39 +4203,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4647,39 +4252,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4699,39 +4304,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>The Accelerate 2026 agenda got even better. See what's new.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
@@ -4749,39 +4354,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4801,39 +4406,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Discover sessions built for growing businesses, and save $200</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
@@ -4846,39 +4451,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4898,39 +4503,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4947,39 +4552,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5003,39 +4608,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -5051,39 +4656,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -5098,39 +4703,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5150,39 +4755,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5206,39 +4811,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1:1 expert access, new AI tools, and $200 off—register now</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
@@ -5254,40 +4859,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -5301,39 +4906,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -5349,39 +4954,139 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -5398,39 +5103,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5448,39 +5153,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -5498,39 +5203,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5549,39 +5254,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -5600,39 +5305,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -5662,39 +5367,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:44:09 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>cscompliance-docreview-seller@amazon.de</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Problem gelöst (Anfrage Nr.: 13280404852)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 Problem gelöst (Anfrage Nr.: 13280404852)
@@ -5716,41 +5421,41 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:42:38 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY,
  MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document
  Review</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5768,40 +5473,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 08:56:32 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5826,39 +5531,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -5885,40 +5590,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Submit proof of insurance by January 18 to avoid listing
  deactivation</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -5934,40 +5639,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -5986,39 +5691,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -6040,39 +5745,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6090,39 +5795,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6140,39 +5845,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 08:06:37 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6190,39 +5895,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 17:08:09 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6240,39 +5945,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:07:40 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6290,39 +5995,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:40 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6341,39 +6046,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:40:10 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -6386,39 +6091,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:27 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6437,39 +6142,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:04 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6487,39 +6192,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:08:31 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6536,39 +6241,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:59:58 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6586,39 +6291,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:32 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6636,39 +6341,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6684,39 +6389,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6734,39 +6439,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6784,39 +6489,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 13:10:03 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6833,39 +6538,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:30:25 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6883,39 +6588,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:14:40 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6933,39 +6638,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 12:45:43 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6981,39 +6686,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 20:11:48 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7031,39 +6736,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 19:56:44 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7078,6 +6783,294 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
 -
  If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:10:17 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:09:41 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:09:40 +0000</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:09:39 +0000</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:09:28 +0000</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 01:08:10 +0000</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
         </is>
       </c>
     </row>
@@ -12628,21 +12621,132 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
+          <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr"/>
       <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- 4sQeBGpWIe
+ Unsellable Products:
+- FNSKU: B0DRCB74YN Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-10-08</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-08 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRC8LPGS Quantity: 1
+- FNSKU: B0DRCC2H56 Quantity: 2
+- FNSKU: B0DRCF83VZ Quantity: 2
+- FNSKU: B0H11DGDRL Quantity: 2
+- FNSKU: X0023C0TBV Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inv</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -12657,39 +12761,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:29:10 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-01</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12710,39 +12814,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 03:52:36 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12766,39 +12870,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:54:38 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -12810,40 +12914,40 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 09:46:06 +0000</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12862,39 +12966,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:18:39 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-24</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12917,40 +13021,40 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:43:34 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12968,40 +13072,40 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:37:46 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -13017,39 +13121,39 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 04:16:10 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-17</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -13073,39 +13177,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 03:24:10 +0000</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -13128,39 +13232,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13189,39 +13293,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -13243,39 +13347,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13303,40 +13407,40 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -13351,39 +13455,39 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13411,39 +13515,39 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E254" s="2" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F254" s="2" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -13459,39 +13563,39 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E255" s="2" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -13514,39 +13618,39 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E256" s="2" t="inlineStr">
+      <c r="E258" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13574,39 +13678,39 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E257" s="2" t="inlineStr">
+      <c r="E259" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -13621,40 +13725,40 @@
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E258" s="2" t="inlineStr">
+      <c r="E260" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
